--- a/Age_Category.xlsx
+++ b/Age_Category.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juanm\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{070828AC-07EB-4841-B403-1C4B292883D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C99B9BA7-0689-4EDB-B640-9859AFCA0000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F1441AC-29AD-4D3B-8FB9-A8477E74C626}"/>
+    <workbookView xWindow="5310" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{1F1441AC-29AD-4D3B-8FB9-A8477E74C626}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="29">
   <si>
     <t>0-4 years old</t>
   </si>
@@ -117,6 +117,12 @@
   </si>
   <si>
     <t>100 years old and over</t>
+  </si>
+  <si>
+    <t>Years</t>
+  </si>
+  <si>
+    <t>Age_Category</t>
   </si>
 </sst>
 </file>
@@ -488,7 +494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{657C4153-A5E3-4CC1-AF0C-645E2325AE46}">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -497,31 +503,31 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
@@ -529,15 +535,15 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
@@ -545,15 +551,15 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
@@ -561,7 +567,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
@@ -569,7 +575,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
@@ -577,7 +583,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
         <v>10</v>
@@ -585,7 +591,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
         <v>10</v>
@@ -593,7 +599,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
@@ -601,15 +607,15 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B15" t="s">
         <v>17</v>
@@ -617,7 +623,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
         <v>17</v>
@@ -625,7 +631,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
         <v>17</v>
@@ -633,7 +639,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B18" t="s">
         <v>17</v>
@@ -641,7 +647,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B19" t="s">
         <v>17</v>
@@ -649,7 +655,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B20" t="s">
         <v>17</v>
@@ -657,9 +663,17 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>26</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B22" t="s">
         <v>17</v>
       </c>
     </row>

--- a/Age_Category.xlsx
+++ b/Age_Category.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juanm\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C99B9BA7-0689-4EDB-B640-9859AFCA0000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE7BBDE7-8C39-4D62-8757-649E93BE4CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5310" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{1F1441AC-29AD-4D3B-8FB9-A8477E74C626}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="31">
   <si>
     <t>0-4 years old</t>
   </si>
@@ -123,6 +123,12 @@
   </si>
   <si>
     <t>Age_Category</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>TOTAL AGES</t>
   </si>
 </sst>
 </file>
@@ -494,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{657C4153-A5E3-4CC1-AF0C-645E2325AE46}">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -677,6 +683,14 @@
         <v>17</v>
       </c>
     </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Age_Category.xlsx
+++ b/Age_Category.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juanm\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE7BBDE7-8C39-4D62-8757-649E93BE4CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{185E7278-1490-4F79-A40E-809EC72FAA15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5310" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{1F1441AC-29AD-4D3B-8FB9-A8477E74C626}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F1441AC-29AD-4D3B-8FB9-A8477E74C626}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,87 +38,24 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="31">
   <si>
-    <t>0-4 years old</t>
-  </si>
-  <si>
     <t>Child</t>
   </si>
   <si>
-    <t>05-09 years old</t>
-  </si>
-  <si>
-    <t>10-14 years old</t>
-  </si>
-  <si>
     <t>Teen</t>
   </si>
   <si>
-    <t>15-19 years old</t>
-  </si>
-  <si>
-    <t>20-24 years old</t>
-  </si>
-  <si>
     <t>Young adult</t>
   </si>
   <si>
-    <t>25-29 years old</t>
-  </si>
-  <si>
-    <t>30-34 years old</t>
-  </si>
-  <si>
     <t>Adult</t>
   </si>
   <si>
-    <t>35-39 years old</t>
-  </si>
-  <si>
-    <t>40-44 years old</t>
-  </si>
-  <si>
-    <t>45-49 years old</t>
-  </si>
-  <si>
-    <t>50-54 years old</t>
-  </si>
-  <si>
-    <t>55-59 years old</t>
-  </si>
-  <si>
-    <t>60-64 years old</t>
-  </si>
-  <si>
     <t>Old age</t>
   </si>
   <si>
     <t>Baby</t>
   </si>
   <si>
-    <t>65-69 years old</t>
-  </si>
-  <si>
-    <t>70-74 years old</t>
-  </si>
-  <si>
-    <t>75-79 years old</t>
-  </si>
-  <si>
-    <t>80-84 years old</t>
-  </si>
-  <si>
-    <t>85-89 years old</t>
-  </si>
-  <si>
-    <t>90-94 years old</t>
-  </si>
-  <si>
-    <t>95-99 years old</t>
-  </si>
-  <si>
-    <t>100 years old and over</t>
-  </si>
-  <si>
     <t>Years</t>
   </si>
   <si>
@@ -129,6 +66,69 @@
   </si>
   <si>
     <t>TOTAL AGES</t>
+  </si>
+  <si>
+    <t>0-4</t>
+  </si>
+  <si>
+    <t>05-09</t>
+  </si>
+  <si>
+    <t>10-14</t>
+  </si>
+  <si>
+    <t>15-19</t>
+  </si>
+  <si>
+    <t>20-24</t>
+  </si>
+  <si>
+    <t>25-29</t>
+  </si>
+  <si>
+    <t>30-34</t>
+  </si>
+  <si>
+    <t>35-39</t>
+  </si>
+  <si>
+    <t>40-44</t>
+  </si>
+  <si>
+    <t>45-49</t>
+  </si>
+  <si>
+    <t>50-54</t>
+  </si>
+  <si>
+    <t>55-59</t>
+  </si>
+  <si>
+    <t>60-64</t>
+  </si>
+  <si>
+    <t>65-69</t>
+  </si>
+  <si>
+    <t>70-74</t>
+  </si>
+  <si>
+    <t>75-79</t>
+  </si>
+  <si>
+    <t>80-84</t>
+  </si>
+  <si>
+    <t>85-89</t>
+  </si>
+  <si>
+    <t>90-94</t>
+  </si>
+  <si>
+    <t>95-99</t>
+  </si>
+  <si>
+    <t>100 and over</t>
   </si>
 </sst>
 </file>
@@ -164,8 +164,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -509,186 +510,186 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B19" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>24</v>
-      </c>
       <c r="B20" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>25</v>
+      <c r="A21" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>26</v>
+      <c r="A22" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/Age_Category.xlsx
+++ b/Age_Category.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juanm\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{185E7278-1490-4F79-A40E-809EC72FAA15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CD12341-F4F0-46FC-B285-35D198F4E016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F1441AC-29AD-4D3B-8FB9-A8477E74C626}"/>
   </bookViews>
@@ -65,9 +65,6 @@
     <t>Total</t>
   </si>
   <si>
-    <t>TOTAL AGES</t>
-  </si>
-  <si>
     <t>0-4</t>
   </si>
   <si>
@@ -129,6 +126,9 @@
   </si>
   <si>
     <t>100 and over</t>
+  </si>
+  <si>
+    <t>Total Ages</t>
   </si>
 </sst>
 </file>
@@ -518,7 +518,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
@@ -526,7 +526,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
@@ -534,7 +534,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
@@ -542,7 +542,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>1</v>
@@ -550,7 +550,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
         <v>2</v>
@@ -558,7 +558,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
         <v>2</v>
@@ -566,7 +566,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
         <v>3</v>
@@ -574,7 +574,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
         <v>3</v>
@@ -582,7 +582,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
         <v>3</v>
@@ -590,7 +590,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
         <v>3</v>
@@ -598,7 +598,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
         <v>3</v>
@@ -606,7 +606,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
         <v>3</v>
@@ -614,7 +614,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s">
         <v>3</v>
@@ -622,7 +622,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
         <v>4</v>
@@ -630,7 +630,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
         <v>4</v>
@@ -638,7 +638,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" t="s">
         <v>4</v>
@@ -646,7 +646,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" t="s">
         <v>4</v>
@@ -654,7 +654,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" t="s">
         <v>4</v>
@@ -662,7 +662,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" t="s">
         <v>4</v>
@@ -670,7 +670,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" t="s">
         <v>4</v>
@@ -678,7 +678,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" t="s">
         <v>4</v>
@@ -686,7 +686,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="B23" t="s">
         <v>8</v>
